--- a/Hardware-Designing/_Deliverables/Transmitter/BOM/LCSC BOM.xlsx
+++ b/Hardware-Designing/_Deliverables/Transmitter/BOM/LCSC BOM.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="101">
   <si>
     <t>Bill of Material (BOM) for  Martin Transmitter</t>
   </si>
@@ -275,7 +275,7 @@
     <t>-----------</t>
   </si>
   <si>
-    <t>AliE</t>
+    <t xml:space="preserve">Local Supplier </t>
   </si>
   <si>
     <t>high current power charging wireless IC chip</t>
@@ -285,9 +285,6 @@
   </si>
   <si>
     <t>XKT-335</t>
-  </si>
-  <si>
-    <t>available 5 pieces per lot only</t>
   </si>
   <si>
     <t>Connectors</t>
@@ -334,12 +331,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="6">
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="&quot;$&quot;#,##0.00000"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="178" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    <numFmt numFmtId="179" formatCode="&quot;$&quot;#,##0.00000"/>
   </numFmts>
   <fonts count="30">
     <font>
@@ -358,6 +355,7 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
@@ -434,6 +432,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
@@ -442,6 +447,37 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -455,25 +491,27 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="3"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -487,48 +525,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -540,7 +539,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
@@ -595,79 +593,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -679,97 +767,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1000,15 +998,6 @@
       </top>
       <bottom style="medium">
         <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1024,21 +1013,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1091,6 +1065,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -1101,13 +1090,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1126,129 +1124,129 @@
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="23" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="21" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1331,8 +1329,8 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1341,10 +1339,10 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="7" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1353,10 +1351,10 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="7" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1365,10 +1363,10 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1380,64 +1378,61 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="6" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="12" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="4" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="7" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="4" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="11" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="12" fillId="5" borderId="0" xfId="23" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="12" fillId="5" borderId="0" xfId="23" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1826,7 +1821,7 @@
     <col min="11" max="11" width="21.8571428571429" customWidth="1"/>
     <col min="12" max="12" width="14.2857142857143" customWidth="1"/>
     <col min="13" max="13" width="11.4285714285714" customWidth="1"/>
-    <col min="14" max="14" width="12.8571428571429" customWidth="1"/>
+    <col min="14" max="14" width="14.2857142857143" customWidth="1"/>
     <col min="15" max="15" width="12.4285714285714" customWidth="1"/>
     <col min="16" max="17" width="13.4285714285714" customWidth="1"/>
     <col min="18" max="18" width="20.5714285714286" customWidth="1"/>
@@ -1856,7 +1851,7 @@
       <c r="Q1" s="2"/>
       <c r="R1" s="2"/>
       <c r="S1" s="2"/>
-      <c r="T1" s="53"/>
+      <c r="T1" s="52"/>
     </row>
     <row r="2" ht="16.5" spans="1:20">
       <c r="A2" s="3" t="s">
@@ -1913,30 +1908,30 @@
       <c r="R2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="S2" s="53" t="s">
+      <c r="S2" s="52" t="s">
         <v>19</v>
       </c>
       <c r="T2" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" ht="15.75" spans="1:20">
+    <row r="3" spans="1:20">
       <c r="A3" s="5">
         <v>1</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="67" t="s">
+      <c r="C3" s="66" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="68" t="s">
+      <c r="D3" s="67" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="68" t="s">
+      <c r="E3" s="67" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="68" t="s">
+      <c r="F3" s="67" t="s">
         <v>25</v>
       </c>
       <c r="G3" s="8" t="s">
@@ -1945,10 +1940,10 @@
       <c r="H3" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I3" s="69" t="s">
+      <c r="I3" s="68" t="s">
         <v>28</v>
       </c>
-      <c r="J3" s="68" t="s">
+      <c r="J3" s="67" t="s">
         <v>29</v>
       </c>
       <c r="K3" s="8">
@@ -1978,27 +1973,27 @@
       <c r="R3" s="32">
         <v>0.0014</v>
       </c>
-      <c r="S3" s="54">
+      <c r="S3" s="53">
         <f>R3*L3</f>
         <v>0.14</v>
       </c>
-      <c r="T3" s="55"/>
+      <c r="T3" s="54"/>
     </row>
-    <row r="4" ht="15.75" spans="1:20">
+    <row r="4" spans="1:20">
       <c r="A4" s="5">
         <v>2</v>
       </c>
       <c r="B4" s="10"/>
-      <c r="C4" s="70" t="s">
+      <c r="C4" s="69" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="71" t="s">
+      <c r="D4" s="70" t="s">
         <v>32</v>
       </c>
-      <c r="E4" s="71" t="s">
+      <c r="E4" s="70" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="72" t="s">
+      <c r="F4" s="71" t="s">
         <v>34</v>
       </c>
       <c r="G4" s="12" t="s">
@@ -2010,7 +2005,7 @@
       <c r="I4" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="J4" s="71" t="s">
+      <c r="J4" s="70" t="s">
         <v>38</v>
       </c>
       <c r="K4" s="12">
@@ -2040,13 +2035,13 @@
       <c r="R4" s="36">
         <v>0.0918</v>
       </c>
-      <c r="S4" s="56">
+      <c r="S4" s="55">
         <f>R4*L4</f>
         <v>0.918</v>
       </c>
-      <c r="T4" s="57"/>
+      <c r="T4" s="56"/>
     </row>
-    <row r="5" ht="15.75" spans="1:20">
+    <row r="5" spans="1:20">
       <c r="A5" s="5">
         <v>3</v>
       </c>
@@ -2054,13 +2049,13 @@
       <c r="C5" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="D5" s="71" t="s">
+      <c r="D5" s="70" t="s">
         <v>40</v>
       </c>
-      <c r="E5" s="71" t="s">
+      <c r="E5" s="70" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="72" t="s">
+      <c r="F5" s="71" t="s">
         <v>41</v>
       </c>
       <c r="G5" s="12" t="s">
@@ -2069,10 +2064,10 @@
       <c r="H5" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="I5" s="73" t="s">
+      <c r="I5" s="72" t="s">
         <v>28</v>
       </c>
-      <c r="J5" s="71" t="s">
+      <c r="J5" s="70" t="s">
         <v>44</v>
       </c>
       <c r="K5" s="12">
@@ -2102,30 +2097,30 @@
       <c r="R5" s="36">
         <v>0.0238</v>
       </c>
-      <c r="S5" s="56">
+      <c r="S5" s="55">
         <f>R5*L5</f>
         <v>0.476</v>
       </c>
-      <c r="T5" s="57"/>
+      <c r="T5" s="56"/>
     </row>
-    <row r="6" ht="15.75" spans="1:20">
+    <row r="6" spans="1:20">
       <c r="A6" s="5">
         <v>4</v>
       </c>
       <c r="B6" s="10"/>
-      <c r="C6" s="70" t="s">
+      <c r="C6" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="D6" s="71" t="s">
+      <c r="D6" s="70" t="s">
         <v>46</v>
       </c>
-      <c r="E6" s="71" t="s">
+      <c r="E6" s="70" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="72" t="s">
+      <c r="F6" s="71" t="s">
         <v>47</v>
       </c>
-      <c r="G6" s="71" t="s">
+      <c r="G6" s="70" t="s">
         <v>48</v>
       </c>
       <c r="H6" s="14" t="s">
@@ -2134,7 +2129,7 @@
       <c r="I6" s="34" t="s">
         <v>50</v>
       </c>
-      <c r="J6" s="71" t="s">
+      <c r="J6" s="70" t="s">
         <v>51</v>
       </c>
       <c r="K6" s="12">
@@ -2164,39 +2159,39 @@
       <c r="R6" s="36">
         <v>0.0037</v>
       </c>
-      <c r="S6" s="56">
+      <c r="S6" s="55">
         <f t="shared" ref="S4:S13" si="3">R6*M6</f>
         <v>0.0185</v>
       </c>
-      <c r="T6" s="57"/>
+      <c r="T6" s="56"/>
     </row>
-    <row r="7" ht="15.75" spans="1:20">
+    <row r="7" spans="1:20">
       <c r="A7" s="5">
         <v>5</v>
       </c>
       <c r="B7" s="16"/>
-      <c r="C7" s="74" t="s">
+      <c r="C7" s="73" t="s">
         <v>52</v>
       </c>
-      <c r="D7" s="75" t="s">
+      <c r="D7" s="74" t="s">
         <v>53</v>
       </c>
-      <c r="E7" s="75" t="s">
+      <c r="E7" s="74" t="s">
         <v>54</v>
       </c>
-      <c r="F7" s="76" t="s">
+      <c r="F7" s="75" t="s">
         <v>55</v>
       </c>
-      <c r="G7" s="75" t="s">
+      <c r="G7" s="74" t="s">
         <v>56</v>
       </c>
       <c r="H7" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="I7" s="77" t="s">
+      <c r="I7" s="76" t="s">
         <v>28</v>
       </c>
-      <c r="J7" s="75" t="s">
+      <c r="J7" s="74" t="s">
         <v>58</v>
       </c>
       <c r="K7" s="18">
@@ -2226,41 +2221,41 @@
       <c r="R7" s="40">
         <v>0.0031</v>
       </c>
-      <c r="S7" s="58">
+      <c r="S7" s="57">
         <f>R7*L7</f>
         <v>0.31</v>
       </c>
-      <c r="T7" s="59"/>
+      <c r="T7" s="58"/>
     </row>
-    <row r="8" ht="15.75" spans="1:20">
+    <row r="8" spans="1:20">
       <c r="A8" s="5">
         <v>6</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="67" t="s">
+      <c r="C8" s="66" t="s">
         <v>60</v>
       </c>
-      <c r="D8" s="68" t="s">
+      <c r="D8" s="67" t="s">
         <v>61</v>
       </c>
-      <c r="E8" s="68" t="s">
+      <c r="E8" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="F8" s="78" t="s">
+      <c r="F8" s="77" t="s">
         <v>63</v>
       </c>
-      <c r="G8" s="68" t="s">
+      <c r="G8" s="67" t="s">
         <v>64</v>
       </c>
       <c r="H8" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="I8" s="68" t="s">
+      <c r="I8" s="67" t="s">
         <v>28</v>
       </c>
-      <c r="J8" s="68" t="s">
+      <c r="J8" s="67" t="s">
         <v>66</v>
       </c>
       <c r="K8" s="8">
@@ -2290,39 +2285,39 @@
       <c r="R8" s="32">
         <v>0.006</v>
       </c>
-      <c r="S8" s="54">
+      <c r="S8" s="53">
         <f t="shared" si="3"/>
         <v>0.06</v>
       </c>
-      <c r="T8" s="55"/>
+      <c r="T8" s="54"/>
     </row>
-    <row r="9" ht="15.75" spans="1:20">
+    <row r="9" spans="1:20">
       <c r="A9" s="5">
         <v>7</v>
       </c>
       <c r="B9" s="10"/>
-      <c r="C9" s="70" t="s">
+      <c r="C9" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="D9" s="71" t="s">
+      <c r="D9" s="70" t="s">
         <v>68</v>
       </c>
-      <c r="E9" s="71" t="s">
+      <c r="E9" s="70" t="s">
         <v>62</v>
       </c>
-      <c r="F9" s="72" t="s">
+      <c r="F9" s="71" t="s">
         <v>69</v>
       </c>
-      <c r="G9" s="71" t="s">
+      <c r="G9" s="70" t="s">
         <v>56</v>
       </c>
       <c r="H9" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="I9" s="71" t="s">
+      <c r="I9" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="J9" s="71" t="s">
+      <c r="J9" s="70" t="s">
         <v>71</v>
       </c>
       <c r="K9" s="12">
@@ -2352,30 +2347,30 @@
       <c r="R9" s="36">
         <v>0.0016</v>
       </c>
-      <c r="S9" s="56">
+      <c r="S9" s="55">
         <f t="shared" si="3"/>
         <v>0.008</v>
       </c>
-      <c r="T9" s="57"/>
+      <c r="T9" s="56"/>
     </row>
-    <row r="10" ht="15.75" spans="1:20">
+    <row r="10" spans="1:20">
       <c r="A10" s="5">
         <v>8</v>
       </c>
       <c r="B10" s="16"/>
-      <c r="C10" s="74" t="s">
+      <c r="C10" s="73" t="s">
         <v>72</v>
       </c>
-      <c r="D10" s="75" t="s">
+      <c r="D10" s="74" t="s">
         <v>73</v>
       </c>
-      <c r="E10" s="75" t="s">
+      <c r="E10" s="74" t="s">
         <v>62</v>
       </c>
-      <c r="F10" s="76" t="s">
+      <c r="F10" s="75" t="s">
         <v>74</v>
       </c>
-      <c r="G10" s="75" t="s">
+      <c r="G10" s="74" t="s">
         <v>64</v>
       </c>
       <c r="H10" s="20" t="s">
@@ -2384,7 +2379,7 @@
       <c r="I10" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="J10" s="75" t="s">
+      <c r="J10" s="74" t="s">
         <v>77</v>
       </c>
       <c r="K10" s="18">
@@ -2414,11 +2409,11 @@
       <c r="R10" s="40">
         <v>0.0022</v>
       </c>
-      <c r="S10" s="58">
+      <c r="S10" s="57">
         <f t="shared" si="3"/>
         <v>0.022</v>
       </c>
-      <c r="T10" s="59"/>
+      <c r="T10" s="58"/>
     </row>
     <row r="11" ht="15.75" spans="1:20">
       <c r="A11" s="5">
@@ -2427,33 +2422,33 @@
       <c r="B11" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="C11" s="79" t="s">
+      <c r="C11" s="78" t="s">
         <v>79</v>
       </c>
-      <c r="D11" s="80" t="s">
+      <c r="D11" s="79" t="s">
         <v>80</v>
       </c>
-      <c r="E11" s="80" t="s">
+      <c r="E11" s="79" t="s">
         <v>81</v>
       </c>
-      <c r="F11" s="80" t="s">
+      <c r="F11" s="79" t="s">
         <v>82</v>
       </c>
-      <c r="G11" s="80" t="s">
+      <c r="G11" s="79" t="s">
         <v>28</v>
       </c>
       <c r="H11" s="23"/>
-      <c r="I11" s="80" t="s">
+      <c r="I11" s="79" t="s">
         <v>28</v>
       </c>
-      <c r="J11" s="80" t="s">
+      <c r="J11" s="79" t="s">
         <v>83</v>
       </c>
       <c r="K11" s="23">
         <v>1</v>
       </c>
       <c r="L11" s="23">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M11" s="23">
         <f t="shared" si="2"/>
@@ -2463,116 +2458,114 @@
         <v>84</v>
       </c>
       <c r="O11" s="45">
-        <v>1.01</v>
+        <v>0.315</v>
       </c>
       <c r="P11" s="45">
         <f t="shared" si="0"/>
-        <v>1.01</v>
+        <v>0.315</v>
       </c>
       <c r="Q11" s="45">
         <f t="shared" si="1"/>
-        <v>5.05</v>
+        <v>2.52</v>
       </c>
       <c r="R11" s="45">
-        <v>1.01</v>
+        <v>0.315</v>
       </c>
       <c r="S11" s="45">
         <f t="shared" si="3"/>
-        <v>5.05</v>
-      </c>
-      <c r="T11" s="60"/>
+        <v>1.575</v>
+      </c>
+      <c r="T11" s="59"/>
     </row>
     <row r="12" ht="15.75" spans="1:20">
       <c r="A12" s="5">
         <v>10</v>
       </c>
       <c r="B12" s="16"/>
-      <c r="C12" s="81" t="s">
+      <c r="C12" s="80" t="s">
         <v>85</v>
       </c>
-      <c r="D12" s="82" t="s">
+      <c r="D12" s="81" t="s">
         <v>86</v>
       </c>
-      <c r="E12" s="82" t="s">
+      <c r="E12" s="81" t="s">
         <v>81</v>
       </c>
-      <c r="F12" s="82" t="s">
+      <c r="F12" s="81" t="s">
         <v>87</v>
       </c>
-      <c r="G12" s="82" t="s">
+      <c r="G12" s="81" t="s">
         <v>28</v>
       </c>
       <c r="H12" s="25"/>
-      <c r="I12" s="82" t="s">
+      <c r="I12" s="81" t="s">
         <v>28</v>
       </c>
-      <c r="J12" s="82" t="s">
+      <c r="J12" s="81" t="s">
         <v>83</v>
       </c>
       <c r="K12" s="25">
         <v>1</v>
       </c>
       <c r="L12" s="25">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M12" s="25">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="N12" s="46" t="s">
+      <c r="N12" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="O12" s="47">
-        <v>0.7</v>
-      </c>
-      <c r="P12" s="47">
+      <c r="O12" s="46">
+        <v>0.315</v>
+      </c>
+      <c r="P12" s="46">
         <f t="shared" si="0"/>
-        <v>0.7</v>
-      </c>
-      <c r="Q12" s="47">
+        <v>0.315</v>
+      </c>
+      <c r="Q12" s="46">
         <f t="shared" si="1"/>
-        <v>3.5</v>
-      </c>
-      <c r="R12" s="47">
-        <v>0.7</v>
-      </c>
-      <c r="S12" s="47">
+        <v>2.52</v>
+      </c>
+      <c r="R12" s="46">
+        <v>0.315</v>
+      </c>
+      <c r="S12" s="46">
         <f t="shared" si="3"/>
-        <v>3.5</v>
-      </c>
-      <c r="T12" s="61" t="s">
-        <v>88</v>
-      </c>
+        <v>1.575</v>
+      </c>
+      <c r="T12" s="60"/>
     </row>
-    <row r="13" ht="15.75" spans="1:20">
+    <row r="13" spans="1:20">
       <c r="A13" s="5">
         <v>11</v>
       </c>
       <c r="B13" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C13" s="66" t="s">
         <v>89</v>
       </c>
-      <c r="C13" s="67" t="s">
+      <c r="D13" s="67" t="s">
         <v>90</v>
       </c>
-      <c r="D13" s="68" t="s">
+      <c r="E13" s="67" t="s">
         <v>91</v>
       </c>
-      <c r="E13" s="68" t="s">
+      <c r="F13" s="67" t="s">
         <v>92</v>
       </c>
-      <c r="F13" s="68" t="s">
+      <c r="G13" s="67" t="s">
         <v>93</v>
       </c>
-      <c r="G13" s="68" t="s">
+      <c r="H13" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="H13" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="I13" s="68" t="s">
+      <c r="I13" s="67" t="s">
         <v>28</v>
       </c>
-      <c r="J13" s="68" t="s">
+      <c r="J13" s="67" t="s">
         <v>83</v>
       </c>
       <c r="K13" s="8">
@@ -2602,37 +2595,37 @@
       <c r="R13" s="33">
         <v>2.5355</v>
       </c>
-      <c r="S13" s="54">
+      <c r="S13" s="53">
         <f t="shared" si="3"/>
         <v>12.6775</v>
       </c>
-      <c r="T13" s="62"/>
+      <c r="T13" s="61"/>
     </row>
-    <row r="14" ht="15.75" spans="1:20">
+    <row r="14" spans="1:20">
       <c r="A14" s="5">
         <v>12</v>
       </c>
       <c r="B14" s="16"/>
-      <c r="C14" s="83" t="s">
+      <c r="C14" s="82" t="s">
+        <v>95</v>
+      </c>
+      <c r="D14" s="83" t="s">
         <v>96</v>
       </c>
-      <c r="D14" s="84" t="s">
+      <c r="E14" s="83" t="s">
+        <v>91</v>
+      </c>
+      <c r="F14" s="83" t="s">
         <v>97</v>
       </c>
-      <c r="E14" s="84" t="s">
-        <v>92</v>
-      </c>
-      <c r="F14" s="84" t="s">
-        <v>98</v>
-      </c>
-      <c r="G14" s="84" t="s">
+      <c r="G14" s="83" t="s">
         <v>28</v>
       </c>
       <c r="H14" s="27"/>
-      <c r="I14" s="84" t="s">
+      <c r="I14" s="83" t="s">
         <v>28</v>
       </c>
-      <c r="J14" s="84" t="s">
+      <c r="J14" s="83" t="s">
         <v>28</v>
       </c>
       <c r="K14" s="27">
@@ -2643,22 +2636,22 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="N14" s="84" t="s">
+      <c r="N14" s="83" t="s">
         <v>28</v>
       </c>
-      <c r="O14" s="84" t="s">
+      <c r="O14" s="83" t="s">
         <v>28</v>
       </c>
-      <c r="P14" s="84" t="s">
+      <c r="P14" s="83" t="s">
         <v>28</v>
       </c>
       <c r="Q14" s="27"/>
       <c r="R14" s="27"/>
-      <c r="S14" s="84" t="s">
+      <c r="S14" s="83" t="s">
         <v>28</v>
       </c>
-      <c r="T14" s="63" t="s">
-        <v>99</v>
+      <c r="T14" s="62" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="15" ht="19.5" spans="1:20">
@@ -2671,23 +2664,23 @@
       <c r="G15" s="28"/>
       <c r="H15" s="28"/>
       <c r="I15" s="28"/>
-      <c r="J15" s="48"/>
-      <c r="K15" s="49" t="s">
-        <v>100</v>
-      </c>
-      <c r="L15" s="49"/>
-      <c r="M15" s="49"/>
-      <c r="N15" s="49"/>
-      <c r="O15" s="49"/>
-      <c r="P15" s="50"/>
-      <c r="Q15" s="50">
+      <c r="J15" s="47"/>
+      <c r="K15" s="48" t="s">
+        <v>99</v>
+      </c>
+      <c r="L15" s="48"/>
+      <c r="M15" s="48"/>
+      <c r="N15" s="48"/>
+      <c r="O15" s="48"/>
+      <c r="P15" s="49"/>
+      <c r="Q15" s="49">
         <f>SUM(Q3:Q13)</f>
-        <v>29.0075</v>
+        <v>25.4975</v>
       </c>
       <c r="R15" s="28"/>
-      <c r="S15" s="64">
+      <c r="S15" s="63">
         <f>SUM(S3:S13)</f>
-        <v>23.18</v>
+        <v>17.78</v>
       </c>
       <c r="T15" s="28"/>
     </row>
@@ -2701,23 +2694,23 @@
       <c r="G16" s="28"/>
       <c r="H16" s="28"/>
       <c r="I16" s="28"/>
-      <c r="J16" s="48"/>
-      <c r="K16" s="51" t="s">
-        <v>101</v>
-      </c>
-      <c r="L16" s="51"/>
-      <c r="M16" s="51"/>
-      <c r="N16" s="51"/>
-      <c r="O16" s="51"/>
-      <c r="P16" s="52">
+      <c r="J16" s="47"/>
+      <c r="K16" s="50" t="s">
+        <v>100</v>
+      </c>
+      <c r="L16" s="50"/>
+      <c r="M16" s="50"/>
+      <c r="N16" s="50"/>
+      <c r="O16" s="50"/>
+      <c r="P16" s="51">
         <f>SUM(P3:P13)</f>
-        <v>5.3431</v>
-      </c>
-      <c r="Q16" s="65"/>
+        <v>4.2631</v>
+      </c>
+      <c r="Q16" s="64"/>
       <c r="R16" s="28"/>
-      <c r="S16" s="66">
+      <c r="S16" s="65">
         <f>S15/5</f>
-        <v>4.636</v>
+        <v>3.556</v>
       </c>
       <c r="T16" s="28"/>
     </row>
@@ -2740,7 +2733,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{347b69da-bb67-452d-a283-4673fe5df1cd}</x14:id>
+          <x14:id>{55ccaec5-5076-4e34-98ac-868c8767e9fe}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -2766,7 +2759,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d7f6b7c0-a146-4db8-a500-c9fe787c2788}</x14:id>
+          <x14:id>{7e960627-908d-4df9-813a-60dbe76f3a31}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -2780,7 +2773,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2c156d80-f61d-429c-8bc2-faecc7246d7a}</x14:id>
+          <x14:id>{ca1fbcf2-fde1-4667-9578-d9f3a5152d00}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -2794,7 +2787,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ba5296cf-52a4-4d5e-9e99-8df06b63a97c}</x14:id>
+          <x14:id>{991bdd40-9112-4a16-b178-5b42bbf1975d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -2804,13 +2797,11 @@
     <hyperlink ref="N8" r:id="rId2" display="LCSC"/>
     <hyperlink ref="N9" r:id="rId3" display="LCSC"/>
     <hyperlink ref="N10" r:id="rId4" display="LCSC"/>
-    <hyperlink ref="N11" r:id="rId5" display="AliE"/>
-    <hyperlink ref="N12" r:id="rId6" display="AliE"/>
-    <hyperlink ref="N13" r:id="rId7" display="LCSC"/>
-    <hyperlink ref="N3" r:id="rId8" display="LCSC"/>
-    <hyperlink ref="N4" r:id="rId9" display="LCSC"/>
-    <hyperlink ref="N5" r:id="rId10" display="LCSC"/>
-    <hyperlink ref="N6" r:id="rId11" display="LCSC"/>
+    <hyperlink ref="N13" r:id="rId5" display="LCSC"/>
+    <hyperlink ref="N3" r:id="rId6" display="LCSC"/>
+    <hyperlink ref="N4" r:id="rId7" display="LCSC"/>
+    <hyperlink ref="N5" r:id="rId8" display="LCSC"/>
+    <hyperlink ref="N6" r:id="rId9" display="LCSC"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait"/>
@@ -2819,7 +2810,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{347b69da-bb67-452d-a283-4673fe5df1cd}">
+          <x14:cfRule type="dataBar" id="{55ccaec5-5076-4e34-98ac-868c8767e9fe}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -2832,7 +2823,7 @@
           <xm:sqref>P16:Q16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d7f6b7c0-a146-4db8-a500-c9fe787c2788}">
+          <x14:cfRule type="dataBar" id="{7e960627-908d-4df9-813a-60dbe76f3a31}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -2845,7 +2836,7 @@
           <xm:sqref>P3:P13</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2c156d80-f61d-429c-8bc2-faecc7246d7a}">
+          <x14:cfRule type="dataBar" id="{ca1fbcf2-fde1-4667-9578-d9f3a5152d00}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -2858,7 +2849,7 @@
           <xm:sqref>S3:S13</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ba5296cf-52a4-4d5e-9e99-8df06b63a97c}">
+          <x14:cfRule type="dataBar" id="{991bdd40-9112-4a16-b178-5b42bbf1975d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
